--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-11 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-12 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04527999877929687</v>
+        <v>0.04479000091552734</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-12 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-13 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04486999988555909</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-13 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-14 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-14 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-15 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04468999862670898</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-15 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-16 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04468999862670898</v>
+        <v>0.04425999641418457</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-16 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-17 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04432000160217285</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-17 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-18 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04432000160217285</v>
+        <v>0.04438000202178955</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-18 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04438000202178955</v>
+        <v>0.04375999927520752</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04375999927520752</v>
+        <v>0.04409999847412109</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04409999847412109</v>
+        <v>0.04467000007629394</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04467000007629394</v>
+        <v>0.04480999946594239</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04480999946594239</v>
+        <v>0.044849997</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-04 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-04 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.044849997</v>
+        <v>0.04485000133514404</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04485000133514404</v>
+        <v>0.04577000141143799</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04577000141143799</v>
+        <v>0.04532999992370605</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04532999992370605</v>
+        <v>0.04565000057220459</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04565000057220459</v>
+        <v>0.04568999767303467</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-14 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04586999893188477</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-14 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04586999893188477</v>
+        <v>0.04549000263214111</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04549000263214111</v>
+        <v>0.04572999954223633</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04572999954223633</v>
+        <v>0.04550000190734863</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04550000190734863</v>
+        <v>0.04540999889373779</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04699000358581543</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-24 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04672999858856201</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-24 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04672999858856201</v>
+        <v>0.04678999900817871</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-28 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04647000312805176</v>
+        <v>0.04595999717712403</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-28 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04595999717712403</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-31 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04647000312805176</v>
+        <v>0.04736999988555908</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-31 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04736999988555908</v>
+        <v>0.04744999885559082</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04620999813079834</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04620999813079834</v>
+        <v>0.04668000221252441</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04668000221252441</v>
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04659999847412109</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699999809265137</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-11 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04699999809265137</v>
+        <v>0.04684000015258789</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-11 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04644999980926514</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04644999980926514</v>
+        <v>0.04696000099182129</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-16 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-16 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0472</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.0472</v>
+        <v>0.04719999790191651</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04719999790191651</v>
+        <v>0.04835000038146973</v>
       </c>
     </row>
     <row r="6">
